--- a/Vulnerability Test Results/PrepWiseAI_Security_300_Test_Cases.xlsx
+++ b/Vulnerability Test Results/PrepWiseAI_Security_300_Test_Cases.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1815" uniqueCount="646">
   <si>
     <t>PrepWiseAI — Comprehensive Security Test Matrix</t>
   </si>
@@ -111,9 +111,6 @@
   </si>
   <si>
     <t>Verify protection against Hardcoded Secrets attacks on /api/auth endpoint (Scenario 4)</t>
-  </si>
-  <si>
-    <t>Failed (Vulnerable)</t>
   </si>
   <si>
     <t>SEC_TC_005</t>
@@ -2521,21 +2518,21 @@
         <v>19</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
         <v>34</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>35</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
@@ -2546,16 +2543,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" t="s">
         <v>38</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>39</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>40</v>
-      </c>
-      <c r="D7" t="s">
-        <v>41</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
@@ -2566,16 +2563,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" t="s">
         <v>42</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>43</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>44</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
@@ -2586,16 +2583,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" t="s">
         <v>47</v>
-      </c>
-      <c r="D9" t="s">
-        <v>48</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
@@ -2606,16 +2603,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
         <v>22</v>
       </c>
       <c r="C10" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" t="s">
         <v>50</v>
-      </c>
-      <c r="D10" t="s">
-        <v>51</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
@@ -2626,16 +2623,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" t="s">
         <v>53</v>
-      </c>
-      <c r="D11" t="s">
-        <v>54</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
@@ -2646,16 +2643,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" t="s">
         <v>56</v>
-      </c>
-      <c r="D12" t="s">
-        <v>57</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -2666,16 +2663,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" t="s">
         <v>58</v>
       </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>59</v>
-      </c>
-      <c r="D13" t="s">
-        <v>60</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
@@ -2686,16 +2683,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" t="s">
         <v>61</v>
       </c>
-      <c r="B14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>62</v>
-      </c>
-      <c r="D14" t="s">
-        <v>63</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
@@ -2706,16 +2703,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" t="s">
         <v>64</v>
       </c>
-      <c r="B15" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>65</v>
-      </c>
-      <c r="D15" t="s">
-        <v>66</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
@@ -2726,16 +2723,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
         <v>16</v>
       </c>
       <c r="C16" t="s">
+        <v>67</v>
+      </c>
+      <c r="D16" t="s">
         <v>68</v>
-      </c>
-      <c r="D16" t="s">
-        <v>69</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
@@ -2746,16 +2743,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
         <v>22</v>
       </c>
       <c r="C17" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" t="s">
         <v>71</v>
-      </c>
-      <c r="D17" t="s">
-        <v>72</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
@@ -2766,16 +2763,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
         <v>26</v>
       </c>
       <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
         <v>74</v>
-      </c>
-      <c r="D18" t="s">
-        <v>75</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
@@ -2786,16 +2783,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
         <v>30</v>
       </c>
       <c r="C19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" t="s">
         <v>77</v>
-      </c>
-      <c r="D19" t="s">
-        <v>78</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -2806,16 +2803,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
         <v>79</v>
       </c>
-      <c r="B20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>80</v>
-      </c>
-      <c r="D20" t="s">
-        <v>81</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
@@ -2826,16 +2823,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
         <v>82</v>
       </c>
-      <c r="B21" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>83</v>
-      </c>
-      <c r="D21" t="s">
-        <v>84</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
@@ -2846,16 +2843,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" t="s">
         <v>85</v>
       </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>86</v>
-      </c>
-      <c r="D22" t="s">
-        <v>87</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
@@ -2866,7 +2863,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
         <v>16</v>
@@ -2875,7 +2872,7 @@
         <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
@@ -2886,7 +2883,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B24" t="s">
         <v>22</v>
@@ -2895,7 +2892,7 @@
         <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
@@ -2906,27 +2903,27 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B25" t="s">
         <v>26</v>
       </c>
       <c r="C25" t="s">
+        <v>92</v>
+      </c>
+      <c r="D25" t="s">
         <v>93</v>
       </c>
-      <c r="D25" t="s">
-        <v>94</v>
-      </c>
       <c r="E25" t="s">
         <v>19</v>
       </c>
       <c r="F25" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B26" t="s">
         <v>30</v>
@@ -2935,27 +2932,27 @@
         <v>31</v>
       </c>
       <c r="D26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
       </c>
       <c r="F26" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" t="s">
         <v>97</v>
-      </c>
-      <c r="B27" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27" t="s">
-        <v>98</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
@@ -2966,16 +2963,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" t="s">
         <v>99</v>
-      </c>
-      <c r="B28" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" t="s">
-        <v>40</v>
-      </c>
-      <c r="D28" t="s">
-        <v>100</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
@@ -2986,16 +2983,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>100</v>
+      </c>
+      <c r="B29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" t="s">
         <v>101</v>
-      </c>
-      <c r="B29" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" t="s">
-        <v>102</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
@@ -3006,16 +3003,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B30" t="s">
         <v>16</v>
       </c>
       <c r="C30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
@@ -3026,16 +3023,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B31" t="s">
         <v>22</v>
       </c>
       <c r="C31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
@@ -3046,7 +3043,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B32" t="s">
         <v>26</v>
@@ -3055,7 +3052,7 @@
         <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
@@ -3066,16 +3063,16 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B33" t="s">
         <v>30</v>
       </c>
       <c r="C33" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
@@ -3086,16 +3083,16 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>110</v>
+      </c>
+      <c r="B34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C34" t="s">
+        <v>58</v>
+      </c>
+      <c r="D34" t="s">
         <v>111</v>
-      </c>
-      <c r="B34" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" t="s">
-        <v>59</v>
-      </c>
-      <c r="D34" t="s">
-        <v>112</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
@@ -3106,16 +3103,16 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" t="s">
         <v>113</v>
-      </c>
-      <c r="B35" t="s">
-        <v>39</v>
-      </c>
-      <c r="C35" t="s">
-        <v>62</v>
-      </c>
-      <c r="D35" t="s">
-        <v>114</v>
       </c>
       <c r="E35" t="s">
         <v>19</v>
@@ -3126,16 +3123,16 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" t="s">
         <v>115</v>
-      </c>
-      <c r="B36" t="s">
-        <v>43</v>
-      </c>
-      <c r="C36" t="s">
-        <v>65</v>
-      </c>
-      <c r="D36" t="s">
-        <v>116</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
@@ -3146,16 +3143,16 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B37" t="s">
         <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D37" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
@@ -3166,16 +3163,16 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B38" t="s">
         <v>22</v>
       </c>
       <c r="C38" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D38" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
@@ -3186,16 +3183,16 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B39" t="s">
         <v>26</v>
       </c>
       <c r="C39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D39" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
@@ -3206,16 +3203,16 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B40" t="s">
         <v>30</v>
       </c>
       <c r="C40" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D40" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
@@ -3226,16 +3223,16 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>124</v>
+      </c>
+      <c r="B41" t="s">
+        <v>34</v>
+      </c>
+      <c r="C41" t="s">
+        <v>79</v>
+      </c>
+      <c r="D41" t="s">
         <v>125</v>
-      </c>
-      <c r="B41" t="s">
-        <v>35</v>
-      </c>
-      <c r="C41" t="s">
-        <v>80</v>
-      </c>
-      <c r="D41" t="s">
-        <v>126</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
@@ -3246,16 +3243,16 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>126</v>
+      </c>
+      <c r="B42" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" t="s">
+        <v>82</v>
+      </c>
+      <c r="D42" t="s">
         <v>127</v>
-      </c>
-      <c r="B42" t="s">
-        <v>39</v>
-      </c>
-      <c r="C42" t="s">
-        <v>83</v>
-      </c>
-      <c r="D42" t="s">
-        <v>128</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
@@ -3266,16 +3263,16 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>128</v>
+      </c>
+      <c r="B43" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" t="s">
+        <v>85</v>
+      </c>
+      <c r="D43" t="s">
         <v>129</v>
-      </c>
-      <c r="B43" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43" t="s">
-        <v>86</v>
-      </c>
-      <c r="D43" t="s">
-        <v>130</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
@@ -3286,7 +3283,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B44" t="s">
         <v>16</v>
@@ -3295,7 +3292,7 @@
         <v>17</v>
       </c>
       <c r="D44" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E44" t="s">
         <v>19</v>
@@ -3306,7 +3303,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B45" t="s">
         <v>22</v>
@@ -3315,7 +3312,7 @@
         <v>23</v>
       </c>
       <c r="D45" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E45" t="s">
         <v>19</v>
@@ -3326,16 +3323,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B46" t="s">
         <v>26</v>
       </c>
       <c r="C46" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D46" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E46" t="s">
         <v>19</v>
@@ -3346,7 +3343,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B47" t="s">
         <v>30</v>
@@ -3355,27 +3352,27 @@
         <v>31</v>
       </c>
       <c r="D47" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
       </c>
       <c r="F47" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>138</v>
+      </c>
+      <c r="B48" t="s">
+        <v>34</v>
+      </c>
+      <c r="C48" t="s">
+        <v>35</v>
+      </c>
+      <c r="D48" t="s">
         <v>139</v>
-      </c>
-      <c r="B48" t="s">
-        <v>35</v>
-      </c>
-      <c r="C48" t="s">
-        <v>36</v>
-      </c>
-      <c r="D48" t="s">
-        <v>140</v>
       </c>
       <c r="E48" t="s">
         <v>19</v>
@@ -3386,16 +3383,16 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>140</v>
+      </c>
+      <c r="B49" t="s">
+        <v>38</v>
+      </c>
+      <c r="C49" t="s">
+        <v>39</v>
+      </c>
+      <c r="D49" t="s">
         <v>141</v>
-      </c>
-      <c r="B49" t="s">
-        <v>39</v>
-      </c>
-      <c r="C49" t="s">
-        <v>40</v>
-      </c>
-      <c r="D49" t="s">
-        <v>142</v>
       </c>
       <c r="E49" t="s">
         <v>19</v>
@@ -3406,16 +3403,16 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>142</v>
+      </c>
+      <c r="B50" t="s">
+        <v>42</v>
+      </c>
+      <c r="C50" t="s">
+        <v>43</v>
+      </c>
+      <c r="D50" t="s">
         <v>143</v>
-      </c>
-      <c r="B50" t="s">
-        <v>43</v>
-      </c>
-      <c r="C50" t="s">
-        <v>44</v>
-      </c>
-      <c r="D50" t="s">
-        <v>144</v>
       </c>
       <c r="E50" t="s">
         <v>19</v>
@@ -3426,16 +3423,16 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B51" t="s">
         <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D51" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E51" t="s">
         <v>19</v>
@@ -3446,16 +3443,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B52" t="s">
         <v>22</v>
       </c>
       <c r="C52" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D52" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E52" t="s">
         <v>19</v>
@@ -3466,36 +3463,36 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B53" t="s">
         <v>26</v>
       </c>
       <c r="C53" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D53" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E53" t="s">
         <v>19</v>
       </c>
       <c r="F53" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B54" t="s">
         <v>30</v>
       </c>
       <c r="C54" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D54" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E54" t="s">
         <v>19</v>
@@ -3506,16 +3503,16 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>152</v>
+      </c>
+      <c r="B55" t="s">
+        <v>34</v>
+      </c>
+      <c r="C55" t="s">
+        <v>58</v>
+      </c>
+      <c r="D55" t="s">
         <v>153</v>
-      </c>
-      <c r="B55" t="s">
-        <v>35</v>
-      </c>
-      <c r="C55" t="s">
-        <v>59</v>
-      </c>
-      <c r="D55" t="s">
-        <v>154</v>
       </c>
       <c r="E55" t="s">
         <v>19</v>
@@ -3526,16 +3523,16 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>154</v>
+      </c>
+      <c r="B56" t="s">
+        <v>38</v>
+      </c>
+      <c r="C56" t="s">
+        <v>61</v>
+      </c>
+      <c r="D56" t="s">
         <v>155</v>
-      </c>
-      <c r="B56" t="s">
-        <v>39</v>
-      </c>
-      <c r="C56" t="s">
-        <v>62</v>
-      </c>
-      <c r="D56" t="s">
-        <v>156</v>
       </c>
       <c r="E56" t="s">
         <v>19</v>
@@ -3546,16 +3543,16 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>156</v>
+      </c>
+      <c r="B57" t="s">
+        <v>42</v>
+      </c>
+      <c r="C57" t="s">
+        <v>64</v>
+      </c>
+      <c r="D57" t="s">
         <v>157</v>
-      </c>
-      <c r="B57" t="s">
-        <v>43</v>
-      </c>
-      <c r="C57" t="s">
-        <v>65</v>
-      </c>
-      <c r="D57" t="s">
-        <v>158</v>
       </c>
       <c r="E57" t="s">
         <v>19</v>
@@ -3566,16 +3563,16 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B58" t="s">
         <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D58" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E58" t="s">
         <v>19</v>
@@ -3586,16 +3583,16 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B59" t="s">
         <v>22</v>
       </c>
       <c r="C59" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D59" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E59" t="s">
         <v>19</v>
@@ -3606,7 +3603,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B60" t="s">
         <v>26</v>
@@ -3615,7 +3612,7 @@
         <v>27</v>
       </c>
       <c r="D60" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E60" t="s">
         <v>19</v>
@@ -3626,16 +3623,16 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B61" t="s">
         <v>30</v>
       </c>
       <c r="C61" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D61" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E61" t="s">
         <v>19</v>
@@ -3646,16 +3643,16 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>166</v>
+      </c>
+      <c r="B62" t="s">
+        <v>34</v>
+      </c>
+      <c r="C62" t="s">
+        <v>79</v>
+      </c>
+      <c r="D62" t="s">
         <v>167</v>
-      </c>
-      <c r="B62" t="s">
-        <v>35</v>
-      </c>
-      <c r="C62" t="s">
-        <v>80</v>
-      </c>
-      <c r="D62" t="s">
-        <v>168</v>
       </c>
       <c r="E62" t="s">
         <v>19</v>
@@ -3666,16 +3663,16 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>168</v>
+      </c>
+      <c r="B63" t="s">
+        <v>38</v>
+      </c>
+      <c r="C63" t="s">
+        <v>82</v>
+      </c>
+      <c r="D63" t="s">
         <v>169</v>
-      </c>
-      <c r="B63" t="s">
-        <v>39</v>
-      </c>
-      <c r="C63" t="s">
-        <v>83</v>
-      </c>
-      <c r="D63" t="s">
-        <v>170</v>
       </c>
       <c r="E63" t="s">
         <v>19</v>
@@ -3686,16 +3683,16 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>170</v>
+      </c>
+      <c r="B64" t="s">
+        <v>42</v>
+      </c>
+      <c r="C64" t="s">
+        <v>85</v>
+      </c>
+      <c r="D64" t="s">
         <v>171</v>
-      </c>
-      <c r="B64" t="s">
-        <v>43</v>
-      </c>
-      <c r="C64" t="s">
-        <v>86</v>
-      </c>
-      <c r="D64" t="s">
-        <v>172</v>
       </c>
       <c r="E64" t="s">
         <v>19</v>
@@ -3706,7 +3703,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B65" t="s">
         <v>16</v>
@@ -3715,7 +3712,7 @@
         <v>17</v>
       </c>
       <c r="D65" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E65" t="s">
         <v>19</v>
@@ -3726,7 +3723,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B66" t="s">
         <v>22</v>
@@ -3735,7 +3732,7 @@
         <v>23</v>
       </c>
       <c r="D66" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E66" t="s">
         <v>19</v>
@@ -3746,16 +3743,16 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B67" t="s">
         <v>26</v>
       </c>
       <c r="C67" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D67" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E67" t="s">
         <v>19</v>
@@ -3766,7 +3763,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B68" t="s">
         <v>30</v>
@@ -3775,27 +3772,27 @@
         <v>31</v>
       </c>
       <c r="D68" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E68" t="s">
         <v>19</v>
       </c>
       <c r="F68" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>180</v>
+      </c>
+      <c r="B69" t="s">
+        <v>34</v>
+      </c>
+      <c r="C69" t="s">
+        <v>35</v>
+      </c>
+      <c r="D69" t="s">
         <v>181</v>
-      </c>
-      <c r="B69" t="s">
-        <v>35</v>
-      </c>
-      <c r="C69" t="s">
-        <v>36</v>
-      </c>
-      <c r="D69" t="s">
-        <v>182</v>
       </c>
       <c r="E69" t="s">
         <v>19</v>
@@ -3806,16 +3803,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>182</v>
+      </c>
+      <c r="B70" t="s">
+        <v>38</v>
+      </c>
+      <c r="C70" t="s">
+        <v>39</v>
+      </c>
+      <c r="D70" t="s">
         <v>183</v>
-      </c>
-      <c r="B70" t="s">
-        <v>39</v>
-      </c>
-      <c r="C70" t="s">
-        <v>40</v>
-      </c>
-      <c r="D70" t="s">
-        <v>184</v>
       </c>
       <c r="E70" t="s">
         <v>19</v>
@@ -3826,16 +3823,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>184</v>
+      </c>
+      <c r="B71" t="s">
+        <v>42</v>
+      </c>
+      <c r="C71" t="s">
+        <v>43</v>
+      </c>
+      <c r="D71" t="s">
         <v>185</v>
-      </c>
-      <c r="B71" t="s">
-        <v>43</v>
-      </c>
-      <c r="C71" t="s">
-        <v>44</v>
-      </c>
-      <c r="D71" t="s">
-        <v>186</v>
       </c>
       <c r="E71" t="s">
         <v>19</v>
@@ -3846,16 +3843,16 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B72" t="s">
         <v>16</v>
       </c>
       <c r="C72" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D72" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E72" t="s">
         <v>19</v>
@@ -3866,16 +3863,16 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B73" t="s">
         <v>22</v>
       </c>
       <c r="C73" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D73" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E73" t="s">
         <v>19</v>
@@ -3886,16 +3883,16 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B74" t="s">
         <v>26</v>
       </c>
       <c r="C74" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D74" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E74" t="s">
         <v>19</v>
@@ -3906,16 +3903,16 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B75" t="s">
         <v>30</v>
       </c>
       <c r="C75" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D75" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E75" t="s">
         <v>19</v>
@@ -3926,16 +3923,16 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>194</v>
+      </c>
+      <c r="B76" t="s">
+        <v>34</v>
+      </c>
+      <c r="C76" t="s">
+        <v>58</v>
+      </c>
+      <c r="D76" t="s">
         <v>195</v>
-      </c>
-      <c r="B76" t="s">
-        <v>35</v>
-      </c>
-      <c r="C76" t="s">
-        <v>59</v>
-      </c>
-      <c r="D76" t="s">
-        <v>196</v>
       </c>
       <c r="E76" t="s">
         <v>19</v>
@@ -3946,16 +3943,16 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>196</v>
+      </c>
+      <c r="B77" t="s">
+        <v>38</v>
+      </c>
+      <c r="C77" t="s">
+        <v>61</v>
+      </c>
+      <c r="D77" t="s">
         <v>197</v>
-      </c>
-      <c r="B77" t="s">
-        <v>39</v>
-      </c>
-      <c r="C77" t="s">
-        <v>62</v>
-      </c>
-      <c r="D77" t="s">
-        <v>198</v>
       </c>
       <c r="E77" t="s">
         <v>19</v>
@@ -3966,16 +3963,16 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>198</v>
+      </c>
+      <c r="B78" t="s">
+        <v>42</v>
+      </c>
+      <c r="C78" t="s">
+        <v>64</v>
+      </c>
+      <c r="D78" t="s">
         <v>199</v>
-      </c>
-      <c r="B78" t="s">
-        <v>43</v>
-      </c>
-      <c r="C78" t="s">
-        <v>65</v>
-      </c>
-      <c r="D78" t="s">
-        <v>200</v>
       </c>
       <c r="E78" t="s">
         <v>19</v>
@@ -3986,16 +3983,16 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B79" t="s">
         <v>16</v>
       </c>
       <c r="C79" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D79" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E79" t="s">
         <v>19</v>
@@ -4006,16 +4003,16 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B80" t="s">
         <v>22</v>
       </c>
       <c r="C80" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D80" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E80" t="s">
         <v>19</v>
@@ -4026,36 +4023,36 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B81" t="s">
         <v>26</v>
       </c>
       <c r="C81" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D81" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E81" t="s">
         <v>19</v>
       </c>
       <c r="F81" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B82" t="s">
         <v>30</v>
       </c>
       <c r="C82" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D82" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E82" t="s">
         <v>19</v>
@@ -4066,16 +4063,16 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>208</v>
+      </c>
+      <c r="B83" t="s">
+        <v>34</v>
+      </c>
+      <c r="C83" t="s">
+        <v>79</v>
+      </c>
+      <c r="D83" t="s">
         <v>209</v>
-      </c>
-      <c r="B83" t="s">
-        <v>35</v>
-      </c>
-      <c r="C83" t="s">
-        <v>80</v>
-      </c>
-      <c r="D83" t="s">
-        <v>210</v>
       </c>
       <c r="E83" t="s">
         <v>19</v>
@@ -4086,16 +4083,16 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>210</v>
+      </c>
+      <c r="B84" t="s">
+        <v>38</v>
+      </c>
+      <c r="C84" t="s">
+        <v>82</v>
+      </c>
+      <c r="D84" t="s">
         <v>211</v>
-      </c>
-      <c r="B84" t="s">
-        <v>39</v>
-      </c>
-      <c r="C84" t="s">
-        <v>83</v>
-      </c>
-      <c r="D84" t="s">
-        <v>212</v>
       </c>
       <c r="E84" t="s">
         <v>19</v>
@@ -4106,16 +4103,16 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>212</v>
+      </c>
+      <c r="B85" t="s">
+        <v>42</v>
+      </c>
+      <c r="C85" t="s">
+        <v>85</v>
+      </c>
+      <c r="D85" t="s">
         <v>213</v>
-      </c>
-      <c r="B85" t="s">
-        <v>43</v>
-      </c>
-      <c r="C85" t="s">
-        <v>86</v>
-      </c>
-      <c r="D85" t="s">
-        <v>214</v>
       </c>
       <c r="E85" t="s">
         <v>19</v>
@@ -4126,7 +4123,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B86" t="s">
         <v>16</v>
@@ -4135,7 +4132,7 @@
         <v>17</v>
       </c>
       <c r="D86" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E86" t="s">
         <v>19</v>
@@ -4146,7 +4143,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B87" t="s">
         <v>22</v>
@@ -4155,7 +4152,7 @@
         <v>23</v>
       </c>
       <c r="D87" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E87" t="s">
         <v>19</v>
@@ -4166,7 +4163,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B88" t="s">
         <v>26</v>
@@ -4175,7 +4172,7 @@
         <v>27</v>
       </c>
       <c r="D88" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E88" t="s">
         <v>19</v>
@@ -4186,7 +4183,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B89" t="s">
         <v>30</v>
@@ -4195,27 +4192,27 @@
         <v>31</v>
       </c>
       <c r="D89" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E89" t="s">
         <v>19</v>
       </c>
       <c r="F89" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>222</v>
+      </c>
+      <c r="B90" t="s">
+        <v>34</v>
+      </c>
+      <c r="C90" t="s">
+        <v>35</v>
+      </c>
+      <c r="D90" t="s">
         <v>223</v>
-      </c>
-      <c r="B90" t="s">
-        <v>35</v>
-      </c>
-      <c r="C90" t="s">
-        <v>36</v>
-      </c>
-      <c r="D90" t="s">
-        <v>224</v>
       </c>
       <c r="E90" t="s">
         <v>19</v>
@@ -4226,16 +4223,16 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>224</v>
+      </c>
+      <c r="B91" t="s">
+        <v>38</v>
+      </c>
+      <c r="C91" t="s">
+        <v>39</v>
+      </c>
+      <c r="D91" t="s">
         <v>225</v>
-      </c>
-      <c r="B91" t="s">
-        <v>39</v>
-      </c>
-      <c r="C91" t="s">
-        <v>40</v>
-      </c>
-      <c r="D91" t="s">
-        <v>226</v>
       </c>
       <c r="E91" t="s">
         <v>19</v>
@@ -4246,16 +4243,16 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>226</v>
+      </c>
+      <c r="B92" t="s">
+        <v>42</v>
+      </c>
+      <c r="C92" t="s">
+        <v>43</v>
+      </c>
+      <c r="D92" t="s">
         <v>227</v>
-      </c>
-      <c r="B92" t="s">
-        <v>43</v>
-      </c>
-      <c r="C92" t="s">
-        <v>44</v>
-      </c>
-      <c r="D92" t="s">
-        <v>228</v>
       </c>
       <c r="E92" t="s">
         <v>19</v>
@@ -4266,16 +4263,16 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B93" t="s">
         <v>16</v>
       </c>
       <c r="C93" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D93" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E93" t="s">
         <v>19</v>
@@ -4286,16 +4283,16 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B94" t="s">
         <v>22</v>
       </c>
       <c r="C94" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D94" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E94" t="s">
         <v>19</v>
@@ -4306,16 +4303,16 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B95" t="s">
         <v>26</v>
       </c>
       <c r="C95" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D95" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E95" t="s">
         <v>19</v>
@@ -4326,16 +4323,16 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B96" t="s">
         <v>30</v>
       </c>
       <c r="C96" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D96" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E96" t="s">
         <v>19</v>
@@ -4346,16 +4343,16 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>236</v>
+      </c>
+      <c r="B97" t="s">
+        <v>34</v>
+      </c>
+      <c r="C97" t="s">
+        <v>58</v>
+      </c>
+      <c r="D97" t="s">
         <v>237</v>
-      </c>
-      <c r="B97" t="s">
-        <v>35</v>
-      </c>
-      <c r="C97" t="s">
-        <v>59</v>
-      </c>
-      <c r="D97" t="s">
-        <v>238</v>
       </c>
       <c r="E97" t="s">
         <v>19</v>
@@ -4366,16 +4363,16 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
+        <v>238</v>
+      </c>
+      <c r="B98" t="s">
+        <v>38</v>
+      </c>
+      <c r="C98" t="s">
+        <v>61</v>
+      </c>
+      <c r="D98" t="s">
         <v>239</v>
-      </c>
-      <c r="B98" t="s">
-        <v>39</v>
-      </c>
-      <c r="C98" t="s">
-        <v>62</v>
-      </c>
-      <c r="D98" t="s">
-        <v>240</v>
       </c>
       <c r="E98" t="s">
         <v>19</v>
@@ -4386,16 +4383,16 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>240</v>
+      </c>
+      <c r="B99" t="s">
+        <v>42</v>
+      </c>
+      <c r="C99" t="s">
+        <v>64</v>
+      </c>
+      <c r="D99" t="s">
         <v>241</v>
-      </c>
-      <c r="B99" t="s">
-        <v>43</v>
-      </c>
-      <c r="C99" t="s">
-        <v>65</v>
-      </c>
-      <c r="D99" t="s">
-        <v>242</v>
       </c>
       <c r="E99" t="s">
         <v>19</v>
@@ -4406,16 +4403,16 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B100" t="s">
         <v>16</v>
       </c>
       <c r="C100" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D100" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E100" t="s">
         <v>19</v>
@@ -4426,16 +4423,16 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B101" t="s">
         <v>22</v>
       </c>
       <c r="C101" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D101" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E101" t="s">
         <v>19</v>
@@ -4446,16 +4443,16 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B102" t="s">
         <v>26</v>
       </c>
       <c r="C102" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D102" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E102" t="s">
         <v>19</v>
@@ -4466,16 +4463,16 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B103" t="s">
         <v>30</v>
       </c>
       <c r="C103" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D103" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E103" t="s">
         <v>19</v>
@@ -4486,16 +4483,16 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>250</v>
+      </c>
+      <c r="B104" t="s">
+        <v>34</v>
+      </c>
+      <c r="C104" t="s">
+        <v>79</v>
+      </c>
+      <c r="D104" t="s">
         <v>251</v>
-      </c>
-      <c r="B104" t="s">
-        <v>35</v>
-      </c>
-      <c r="C104" t="s">
-        <v>80</v>
-      </c>
-      <c r="D104" t="s">
-        <v>252</v>
       </c>
       <c r="E104" t="s">
         <v>19</v>
@@ -4506,16 +4503,16 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>252</v>
+      </c>
+      <c r="B105" t="s">
+        <v>38</v>
+      </c>
+      <c r="C105" t="s">
+        <v>82</v>
+      </c>
+      <c r="D105" t="s">
         <v>253</v>
-      </c>
-      <c r="B105" t="s">
-        <v>39</v>
-      </c>
-      <c r="C105" t="s">
-        <v>83</v>
-      </c>
-      <c r="D105" t="s">
-        <v>254</v>
       </c>
       <c r="E105" t="s">
         <v>19</v>
@@ -4526,16 +4523,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>254</v>
+      </c>
+      <c r="B106" t="s">
+        <v>42</v>
+      </c>
+      <c r="C106" t="s">
+        <v>85</v>
+      </c>
+      <c r="D106" t="s">
         <v>255</v>
-      </c>
-      <c r="B106" t="s">
-        <v>43</v>
-      </c>
-      <c r="C106" t="s">
-        <v>86</v>
-      </c>
-      <c r="D106" t="s">
-        <v>256</v>
       </c>
       <c r="E106" t="s">
         <v>19</v>
@@ -4546,7 +4543,7 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B107" t="s">
         <v>16</v>
@@ -4555,7 +4552,7 @@
         <v>17</v>
       </c>
       <c r="D107" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E107" t="s">
         <v>19</v>
@@ -4566,7 +4563,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B108" t="s">
         <v>22</v>
@@ -4575,7 +4572,7 @@
         <v>23</v>
       </c>
       <c r="D108" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E108" t="s">
         <v>19</v>
@@ -4586,27 +4583,27 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B109" t="s">
         <v>26</v>
       </c>
       <c r="C109" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D109" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E109" t="s">
         <v>19</v>
       </c>
       <c r="F109" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B110" t="s">
         <v>30</v>
@@ -4615,27 +4612,27 @@
         <v>31</v>
       </c>
       <c r="D110" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E110" t="s">
         <v>19</v>
       </c>
       <c r="F110" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>264</v>
+      </c>
+      <c r="B111" t="s">
+        <v>34</v>
+      </c>
+      <c r="C111" t="s">
+        <v>35</v>
+      </c>
+      <c r="D111" t="s">
         <v>265</v>
-      </c>
-      <c r="B111" t="s">
-        <v>35</v>
-      </c>
-      <c r="C111" t="s">
-        <v>36</v>
-      </c>
-      <c r="D111" t="s">
-        <v>266</v>
       </c>
       <c r="E111" t="s">
         <v>19</v>
@@ -4646,16 +4643,16 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>266</v>
+      </c>
+      <c r="B112" t="s">
+        <v>38</v>
+      </c>
+      <c r="C112" t="s">
+        <v>39</v>
+      </c>
+      <c r="D112" t="s">
         <v>267</v>
-      </c>
-      <c r="B112" t="s">
-        <v>39</v>
-      </c>
-      <c r="C112" t="s">
-        <v>40</v>
-      </c>
-      <c r="D112" t="s">
-        <v>268</v>
       </c>
       <c r="E112" t="s">
         <v>19</v>
@@ -4666,16 +4663,16 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>268</v>
+      </c>
+      <c r="B113" t="s">
+        <v>42</v>
+      </c>
+      <c r="C113" t="s">
+        <v>43</v>
+      </c>
+      <c r="D113" t="s">
         <v>269</v>
-      </c>
-      <c r="B113" t="s">
-        <v>43</v>
-      </c>
-      <c r="C113" t="s">
-        <v>44</v>
-      </c>
-      <c r="D113" t="s">
-        <v>270</v>
       </c>
       <c r="E113" t="s">
         <v>19</v>
@@ -4686,16 +4683,16 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B114" t="s">
         <v>16</v>
       </c>
       <c r="C114" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D114" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E114" t="s">
         <v>19</v>
@@ -4706,16 +4703,16 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B115" t="s">
         <v>22</v>
       </c>
       <c r="C115" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D115" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E115" t="s">
         <v>19</v>
@@ -4726,7 +4723,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B116" t="s">
         <v>26</v>
@@ -4735,7 +4732,7 @@
         <v>27</v>
       </c>
       <c r="D116" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E116" t="s">
         <v>19</v>
@@ -4746,16 +4743,16 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B117" t="s">
         <v>30</v>
       </c>
       <c r="C117" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D117" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E117" t="s">
         <v>19</v>
@@ -4766,16 +4763,16 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
+        <v>278</v>
+      </c>
+      <c r="B118" t="s">
+        <v>34</v>
+      </c>
+      <c r="C118" t="s">
+        <v>58</v>
+      </c>
+      <c r="D118" t="s">
         <v>279</v>
-      </c>
-      <c r="B118" t="s">
-        <v>35</v>
-      </c>
-      <c r="C118" t="s">
-        <v>59</v>
-      </c>
-      <c r="D118" t="s">
-        <v>280</v>
       </c>
       <c r="E118" t="s">
         <v>19</v>
@@ -4786,16 +4783,16 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>280</v>
+      </c>
+      <c r="B119" t="s">
+        <v>38</v>
+      </c>
+      <c r="C119" t="s">
+        <v>61</v>
+      </c>
+      <c r="D119" t="s">
         <v>281</v>
-      </c>
-      <c r="B119" t="s">
-        <v>39</v>
-      </c>
-      <c r="C119" t="s">
-        <v>62</v>
-      </c>
-      <c r="D119" t="s">
-        <v>282</v>
       </c>
       <c r="E119" t="s">
         <v>19</v>
@@ -4806,16 +4803,16 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>282</v>
+      </c>
+      <c r="B120" t="s">
+        <v>42</v>
+      </c>
+      <c r="C120" t="s">
+        <v>64</v>
+      </c>
+      <c r="D120" t="s">
         <v>283</v>
-      </c>
-      <c r="B120" t="s">
-        <v>43</v>
-      </c>
-      <c r="C120" t="s">
-        <v>65</v>
-      </c>
-      <c r="D120" t="s">
-        <v>284</v>
       </c>
       <c r="E120" t="s">
         <v>19</v>
@@ -4826,16 +4823,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B121" t="s">
         <v>16</v>
       </c>
       <c r="C121" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D121" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E121" t="s">
         <v>19</v>
@@ -4846,16 +4843,16 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B122" t="s">
         <v>22</v>
       </c>
       <c r="C122" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D122" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E122" t="s">
         <v>19</v>
@@ -4866,16 +4863,16 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B123" t="s">
         <v>26</v>
       </c>
       <c r="C123" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D123" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E123" t="s">
         <v>19</v>
@@ -4886,16 +4883,16 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B124" t="s">
         <v>30</v>
       </c>
       <c r="C124" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D124" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E124" t="s">
         <v>19</v>
@@ -4906,16 +4903,16 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
+        <v>292</v>
+      </c>
+      <c r="B125" t="s">
+        <v>34</v>
+      </c>
+      <c r="C125" t="s">
+        <v>79</v>
+      </c>
+      <c r="D125" t="s">
         <v>293</v>
-      </c>
-      <c r="B125" t="s">
-        <v>35</v>
-      </c>
-      <c r="C125" t="s">
-        <v>80</v>
-      </c>
-      <c r="D125" t="s">
-        <v>294</v>
       </c>
       <c r="E125" t="s">
         <v>19</v>
@@ -4926,16 +4923,16 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>294</v>
+      </c>
+      <c r="B126" t="s">
+        <v>38</v>
+      </c>
+      <c r="C126" t="s">
+        <v>82</v>
+      </c>
+      <c r="D126" t="s">
         <v>295</v>
-      </c>
-      <c r="B126" t="s">
-        <v>39</v>
-      </c>
-      <c r="C126" t="s">
-        <v>83</v>
-      </c>
-      <c r="D126" t="s">
-        <v>296</v>
       </c>
       <c r="E126" t="s">
         <v>19</v>
@@ -4946,16 +4943,16 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
+        <v>296</v>
+      </c>
+      <c r="B127" t="s">
+        <v>42</v>
+      </c>
+      <c r="C127" t="s">
+        <v>85</v>
+      </c>
+      <c r="D127" t="s">
         <v>297</v>
-      </c>
-      <c r="B127" t="s">
-        <v>43</v>
-      </c>
-      <c r="C127" t="s">
-        <v>86</v>
-      </c>
-      <c r="D127" t="s">
-        <v>298</v>
       </c>
       <c r="E127" t="s">
         <v>19</v>
@@ -4966,7 +4963,7 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B128" t="s">
         <v>16</v>
@@ -4975,7 +4972,7 @@
         <v>17</v>
       </c>
       <c r="D128" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E128" t="s">
         <v>19</v>
@@ -4986,7 +4983,7 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B129" t="s">
         <v>22</v>
@@ -4995,7 +4992,7 @@
         <v>23</v>
       </c>
       <c r="D129" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E129" t="s">
         <v>19</v>
@@ -5006,16 +5003,16 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B130" t="s">
         <v>26</v>
       </c>
       <c r="C130" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D130" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E130" t="s">
         <v>19</v>
@@ -5026,7 +5023,7 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B131" t="s">
         <v>30</v>
@@ -5035,27 +5032,27 @@
         <v>31</v>
       </c>
       <c r="D131" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E131" t="s">
         <v>19</v>
       </c>
       <c r="F131" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
+        <v>306</v>
+      </c>
+      <c r="B132" t="s">
+        <v>34</v>
+      </c>
+      <c r="C132" t="s">
+        <v>35</v>
+      </c>
+      <c r="D132" t="s">
         <v>307</v>
-      </c>
-      <c r="B132" t="s">
-        <v>35</v>
-      </c>
-      <c r="C132" t="s">
-        <v>36</v>
-      </c>
-      <c r="D132" t="s">
-        <v>308</v>
       </c>
       <c r="E132" t="s">
         <v>19</v>
@@ -5066,16 +5063,16 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>308</v>
+      </c>
+      <c r="B133" t="s">
+        <v>38</v>
+      </c>
+      <c r="C133" t="s">
+        <v>39</v>
+      </c>
+      <c r="D133" t="s">
         <v>309</v>
-      </c>
-      <c r="B133" t="s">
-        <v>39</v>
-      </c>
-      <c r="C133" t="s">
-        <v>40</v>
-      </c>
-      <c r="D133" t="s">
-        <v>310</v>
       </c>
       <c r="E133" t="s">
         <v>19</v>
@@ -5086,16 +5083,16 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>310</v>
+      </c>
+      <c r="B134" t="s">
+        <v>42</v>
+      </c>
+      <c r="C134" t="s">
+        <v>43</v>
+      </c>
+      <c r="D134" t="s">
         <v>311</v>
-      </c>
-      <c r="B134" t="s">
-        <v>43</v>
-      </c>
-      <c r="C134" t="s">
-        <v>44</v>
-      </c>
-      <c r="D134" t="s">
-        <v>312</v>
       </c>
       <c r="E134" t="s">
         <v>19</v>
@@ -5106,16 +5103,16 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B135" t="s">
         <v>16</v>
       </c>
       <c r="C135" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D135" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E135" t="s">
         <v>19</v>
@@ -5126,16 +5123,16 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B136" t="s">
         <v>22</v>
       </c>
       <c r="C136" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D136" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E136" t="s">
         <v>19</v>
@@ -5146,36 +5143,36 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B137" t="s">
         <v>26</v>
       </c>
       <c r="C137" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D137" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E137" t="s">
         <v>19</v>
       </c>
       <c r="F137" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B138" t="s">
         <v>30</v>
       </c>
       <c r="C138" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D138" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E138" t="s">
         <v>19</v>
@@ -5186,16 +5183,16 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>320</v>
+      </c>
+      <c r="B139" t="s">
+        <v>34</v>
+      </c>
+      <c r="C139" t="s">
+        <v>58</v>
+      </c>
+      <c r="D139" t="s">
         <v>321</v>
-      </c>
-      <c r="B139" t="s">
-        <v>35</v>
-      </c>
-      <c r="C139" t="s">
-        <v>59</v>
-      </c>
-      <c r="D139" t="s">
-        <v>322</v>
       </c>
       <c r="E139" t="s">
         <v>19</v>
@@ -5206,16 +5203,16 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>322</v>
+      </c>
+      <c r="B140" t="s">
+        <v>38</v>
+      </c>
+      <c r="C140" t="s">
+        <v>61</v>
+      </c>
+      <c r="D140" t="s">
         <v>323</v>
-      </c>
-      <c r="B140" t="s">
-        <v>39</v>
-      </c>
-      <c r="C140" t="s">
-        <v>62</v>
-      </c>
-      <c r="D140" t="s">
-        <v>324</v>
       </c>
       <c r="E140" t="s">
         <v>19</v>
@@ -5226,16 +5223,16 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>324</v>
+      </c>
+      <c r="B141" t="s">
+        <v>42</v>
+      </c>
+      <c r="C141" t="s">
+        <v>64</v>
+      </c>
+      <c r="D141" t="s">
         <v>325</v>
-      </c>
-      <c r="B141" t="s">
-        <v>43</v>
-      </c>
-      <c r="C141" t="s">
-        <v>65</v>
-      </c>
-      <c r="D141" t="s">
-        <v>326</v>
       </c>
       <c r="E141" t="s">
         <v>19</v>
@@ -5246,16 +5243,16 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B142" t="s">
         <v>16</v>
       </c>
       <c r="C142" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D142" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E142" t="s">
         <v>19</v>
@@ -5266,16 +5263,16 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B143" t="s">
         <v>22</v>
       </c>
       <c r="C143" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D143" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E143" t="s">
         <v>19</v>
@@ -5286,7 +5283,7 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B144" t="s">
         <v>26</v>
@@ -5295,7 +5292,7 @@
         <v>27</v>
       </c>
       <c r="D144" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E144" t="s">
         <v>19</v>
@@ -5306,16 +5303,16 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B145" t="s">
         <v>30</v>
       </c>
       <c r="C145" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D145" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E145" t="s">
         <v>19</v>
@@ -5326,16 +5323,16 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
+        <v>334</v>
+      </c>
+      <c r="B146" t="s">
+        <v>34</v>
+      </c>
+      <c r="C146" t="s">
+        <v>79</v>
+      </c>
+      <c r="D146" t="s">
         <v>335</v>
-      </c>
-      <c r="B146" t="s">
-        <v>35</v>
-      </c>
-      <c r="C146" t="s">
-        <v>80</v>
-      </c>
-      <c r="D146" t="s">
-        <v>336</v>
       </c>
       <c r="E146" t="s">
         <v>19</v>
@@ -5346,16 +5343,16 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>336</v>
+      </c>
+      <c r="B147" t="s">
+        <v>38</v>
+      </c>
+      <c r="C147" t="s">
+        <v>82</v>
+      </c>
+      <c r="D147" t="s">
         <v>337</v>
-      </c>
-      <c r="B147" t="s">
-        <v>39</v>
-      </c>
-      <c r="C147" t="s">
-        <v>83</v>
-      </c>
-      <c r="D147" t="s">
-        <v>338</v>
       </c>
       <c r="E147" t="s">
         <v>19</v>
@@ -5366,16 +5363,16 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>338</v>
+      </c>
+      <c r="B148" t="s">
+        <v>42</v>
+      </c>
+      <c r="C148" t="s">
+        <v>85</v>
+      </c>
+      <c r="D148" t="s">
         <v>339</v>
-      </c>
-      <c r="B148" t="s">
-        <v>43</v>
-      </c>
-      <c r="C148" t="s">
-        <v>86</v>
-      </c>
-      <c r="D148" t="s">
-        <v>340</v>
       </c>
       <c r="E148" t="s">
         <v>19</v>
@@ -5386,7 +5383,7 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B149" t="s">
         <v>16</v>
@@ -5395,7 +5392,7 @@
         <v>17</v>
       </c>
       <c r="D149" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E149" t="s">
         <v>19</v>
@@ -5406,7 +5403,7 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B150" t="s">
         <v>22</v>
@@ -5415,7 +5412,7 @@
         <v>23</v>
       </c>
       <c r="D150" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E150" t="s">
         <v>19</v>
@@ -5426,16 +5423,16 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B151" t="s">
         <v>26</v>
       </c>
       <c r="C151" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D151" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E151" t="s">
         <v>19</v>
@@ -5446,7 +5443,7 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B152" t="s">
         <v>30</v>
@@ -5455,27 +5452,27 @@
         <v>31</v>
       </c>
       <c r="D152" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E152" t="s">
         <v>19</v>
       </c>
       <c r="F152" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
+        <v>348</v>
+      </c>
+      <c r="B153" t="s">
+        <v>34</v>
+      </c>
+      <c r="C153" t="s">
+        <v>35</v>
+      </c>
+      <c r="D153" t="s">
         <v>349</v>
-      </c>
-      <c r="B153" t="s">
-        <v>35</v>
-      </c>
-      <c r="C153" t="s">
-        <v>36</v>
-      </c>
-      <c r="D153" t="s">
-        <v>350</v>
       </c>
       <c r="E153" t="s">
         <v>19</v>
@@ -5486,16 +5483,16 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
+        <v>350</v>
+      </c>
+      <c r="B154" t="s">
+        <v>38</v>
+      </c>
+      <c r="C154" t="s">
+        <v>39</v>
+      </c>
+      <c r="D154" t="s">
         <v>351</v>
-      </c>
-      <c r="B154" t="s">
-        <v>39</v>
-      </c>
-      <c r="C154" t="s">
-        <v>40</v>
-      </c>
-      <c r="D154" t="s">
-        <v>352</v>
       </c>
       <c r="E154" t="s">
         <v>19</v>
@@ -5506,16 +5503,16 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
+        <v>352</v>
+      </c>
+      <c r="B155" t="s">
+        <v>42</v>
+      </c>
+      <c r="C155" t="s">
+        <v>43</v>
+      </c>
+      <c r="D155" t="s">
         <v>353</v>
-      </c>
-      <c r="B155" t="s">
-        <v>43</v>
-      </c>
-      <c r="C155" t="s">
-        <v>44</v>
-      </c>
-      <c r="D155" t="s">
-        <v>354</v>
       </c>
       <c r="E155" t="s">
         <v>19</v>
@@ -5526,16 +5523,16 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B156" t="s">
         <v>16</v>
       </c>
       <c r="C156" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D156" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E156" t="s">
         <v>19</v>
@@ -5546,16 +5543,16 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B157" t="s">
         <v>22</v>
       </c>
       <c r="C157" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D157" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E157" t="s">
         <v>19</v>
@@ -5566,16 +5563,16 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B158" t="s">
         <v>26</v>
       </c>
       <c r="C158" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D158" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E158" t="s">
         <v>19</v>
@@ -5586,16 +5583,16 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B159" t="s">
         <v>30</v>
       </c>
       <c r="C159" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D159" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E159" t="s">
         <v>19</v>
@@ -5606,16 +5603,16 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>362</v>
+      </c>
+      <c r="B160" t="s">
+        <v>34</v>
+      </c>
+      <c r="C160" t="s">
+        <v>58</v>
+      </c>
+      <c r="D160" t="s">
         <v>363</v>
-      </c>
-      <c r="B160" t="s">
-        <v>35</v>
-      </c>
-      <c r="C160" t="s">
-        <v>59</v>
-      </c>
-      <c r="D160" t="s">
-        <v>364</v>
       </c>
       <c r="E160" t="s">
         <v>19</v>
@@ -5626,16 +5623,16 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
+        <v>364</v>
+      </c>
+      <c r="B161" t="s">
+        <v>38</v>
+      </c>
+      <c r="C161" t="s">
+        <v>61</v>
+      </c>
+      <c r="D161" t="s">
         <v>365</v>
-      </c>
-      <c r="B161" t="s">
-        <v>39</v>
-      </c>
-      <c r="C161" t="s">
-        <v>62</v>
-      </c>
-      <c r="D161" t="s">
-        <v>366</v>
       </c>
       <c r="E161" t="s">
         <v>19</v>
@@ -5646,16 +5643,16 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>366</v>
+      </c>
+      <c r="B162" t="s">
+        <v>42</v>
+      </c>
+      <c r="C162" t="s">
+        <v>64</v>
+      </c>
+      <c r="D162" t="s">
         <v>367</v>
-      </c>
-      <c r="B162" t="s">
-        <v>43</v>
-      </c>
-      <c r="C162" t="s">
-        <v>65</v>
-      </c>
-      <c r="D162" t="s">
-        <v>368</v>
       </c>
       <c r="E162" t="s">
         <v>19</v>
@@ -5666,16 +5663,16 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B163" t="s">
         <v>16</v>
       </c>
       <c r="C163" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D163" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E163" t="s">
         <v>19</v>
@@ -5686,16 +5683,16 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B164" t="s">
         <v>22</v>
       </c>
       <c r="C164" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D164" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E164" t="s">
         <v>19</v>
@@ -5706,36 +5703,36 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B165" t="s">
         <v>26</v>
       </c>
       <c r="C165" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D165" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E165" t="s">
         <v>19</v>
       </c>
       <c r="F165" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B166" t="s">
         <v>30</v>
       </c>
       <c r="C166" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D166" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E166" t="s">
         <v>19</v>
@@ -5746,16 +5743,16 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
+        <v>376</v>
+      </c>
+      <c r="B167" t="s">
+        <v>34</v>
+      </c>
+      <c r="C167" t="s">
+        <v>79</v>
+      </c>
+      <c r="D167" t="s">
         <v>377</v>
-      </c>
-      <c r="B167" t="s">
-        <v>35</v>
-      </c>
-      <c r="C167" t="s">
-        <v>80</v>
-      </c>
-      <c r="D167" t="s">
-        <v>378</v>
       </c>
       <c r="E167" t="s">
         <v>19</v>
@@ -5766,16 +5763,16 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>378</v>
+      </c>
+      <c r="B168" t="s">
+        <v>38</v>
+      </c>
+      <c r="C168" t="s">
+        <v>82</v>
+      </c>
+      <c r="D168" t="s">
         <v>379</v>
-      </c>
-      <c r="B168" t="s">
-        <v>39</v>
-      </c>
-      <c r="C168" t="s">
-        <v>83</v>
-      </c>
-      <c r="D168" t="s">
-        <v>380</v>
       </c>
       <c r="E168" t="s">
         <v>19</v>
@@ -5786,16 +5783,16 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
+        <v>380</v>
+      </c>
+      <c r="B169" t="s">
+        <v>42</v>
+      </c>
+      <c r="C169" t="s">
+        <v>85</v>
+      </c>
+      <c r="D169" t="s">
         <v>381</v>
-      </c>
-      <c r="B169" t="s">
-        <v>43</v>
-      </c>
-      <c r="C169" t="s">
-        <v>86</v>
-      </c>
-      <c r="D169" t="s">
-        <v>382</v>
       </c>
       <c r="E169" t="s">
         <v>19</v>
@@ -5806,7 +5803,7 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B170" t="s">
         <v>16</v>
@@ -5815,7 +5812,7 @@
         <v>17</v>
       </c>
       <c r="D170" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E170" t="s">
         <v>19</v>
@@ -5826,7 +5823,7 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B171" t="s">
         <v>22</v>
@@ -5835,7 +5832,7 @@
         <v>23</v>
       </c>
       <c r="D171" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E171" t="s">
         <v>19</v>
@@ -5846,7 +5843,7 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B172" t="s">
         <v>26</v>
@@ -5855,7 +5852,7 @@
         <v>27</v>
       </c>
       <c r="D172" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E172" t="s">
         <v>19</v>
@@ -5866,7 +5863,7 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B173" t="s">
         <v>30</v>
@@ -5875,27 +5872,27 @@
         <v>31</v>
       </c>
       <c r="D173" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E173" t="s">
         <v>19</v>
       </c>
       <c r="F173" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>390</v>
+      </c>
+      <c r="B174" t="s">
+        <v>34</v>
+      </c>
+      <c r="C174" t="s">
+        <v>35</v>
+      </c>
+      <c r="D174" t="s">
         <v>391</v>
-      </c>
-      <c r="B174" t="s">
-        <v>35</v>
-      </c>
-      <c r="C174" t="s">
-        <v>36</v>
-      </c>
-      <c r="D174" t="s">
-        <v>392</v>
       </c>
       <c r="E174" t="s">
         <v>19</v>
@@ -5906,16 +5903,16 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>392</v>
+      </c>
+      <c r="B175" t="s">
+        <v>38</v>
+      </c>
+      <c r="C175" t="s">
+        <v>39</v>
+      </c>
+      <c r="D175" t="s">
         <v>393</v>
-      </c>
-      <c r="B175" t="s">
-        <v>39</v>
-      </c>
-      <c r="C175" t="s">
-        <v>40</v>
-      </c>
-      <c r="D175" t="s">
-        <v>394</v>
       </c>
       <c r="E175" t="s">
         <v>19</v>
@@ -5926,16 +5923,16 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>394</v>
+      </c>
+      <c r="B176" t="s">
+        <v>42</v>
+      </c>
+      <c r="C176" t="s">
+        <v>43</v>
+      </c>
+      <c r="D176" t="s">
         <v>395</v>
-      </c>
-      <c r="B176" t="s">
-        <v>43</v>
-      </c>
-      <c r="C176" t="s">
-        <v>44</v>
-      </c>
-      <c r="D176" t="s">
-        <v>396</v>
       </c>
       <c r="E176" t="s">
         <v>19</v>
@@ -5946,16 +5943,16 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B177" t="s">
         <v>16</v>
       </c>
       <c r="C177" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D177" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E177" t="s">
         <v>19</v>
@@ -5966,16 +5963,16 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B178" t="s">
         <v>22</v>
       </c>
       <c r="C178" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D178" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E178" t="s">
         <v>19</v>
@@ -5986,16 +5983,16 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B179" t="s">
         <v>26</v>
       </c>
       <c r="C179" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D179" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E179" t="s">
         <v>19</v>
@@ -6006,16 +6003,16 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B180" t="s">
         <v>30</v>
       </c>
       <c r="C180" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D180" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E180" t="s">
         <v>19</v>
@@ -6026,16 +6023,16 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
+        <v>404</v>
+      </c>
+      <c r="B181" t="s">
+        <v>34</v>
+      </c>
+      <c r="C181" t="s">
+        <v>58</v>
+      </c>
+      <c r="D181" t="s">
         <v>405</v>
-      </c>
-      <c r="B181" t="s">
-        <v>35</v>
-      </c>
-      <c r="C181" t="s">
-        <v>59</v>
-      </c>
-      <c r="D181" t="s">
-        <v>406</v>
       </c>
       <c r="E181" t="s">
         <v>19</v>
@@ -6046,16 +6043,16 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
+        <v>406</v>
+      </c>
+      <c r="B182" t="s">
+        <v>38</v>
+      </c>
+      <c r="C182" t="s">
+        <v>61</v>
+      </c>
+      <c r="D182" t="s">
         <v>407</v>
-      </c>
-      <c r="B182" t="s">
-        <v>39</v>
-      </c>
-      <c r="C182" t="s">
-        <v>62</v>
-      </c>
-      <c r="D182" t="s">
-        <v>408</v>
       </c>
       <c r="E182" t="s">
         <v>19</v>
@@ -6066,16 +6063,16 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
+        <v>408</v>
+      </c>
+      <c r="B183" t="s">
+        <v>42</v>
+      </c>
+      <c r="C183" t="s">
+        <v>64</v>
+      </c>
+      <c r="D183" t="s">
         <v>409</v>
-      </c>
-      <c r="B183" t="s">
-        <v>43</v>
-      </c>
-      <c r="C183" t="s">
-        <v>65</v>
-      </c>
-      <c r="D183" t="s">
-        <v>410</v>
       </c>
       <c r="E183" t="s">
         <v>19</v>
@@ -6086,16 +6083,16 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B184" t="s">
         <v>16</v>
       </c>
       <c r="C184" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D184" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E184" t="s">
         <v>19</v>
@@ -6106,16 +6103,16 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B185" t="s">
         <v>22</v>
       </c>
       <c r="C185" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D185" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E185" t="s">
         <v>19</v>
@@ -6126,16 +6123,16 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B186" t="s">
         <v>26</v>
       </c>
       <c r="C186" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D186" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E186" t="s">
         <v>19</v>
@@ -6146,16 +6143,16 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B187" t="s">
         <v>30</v>
       </c>
       <c r="C187" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D187" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="E187" t="s">
         <v>19</v>
@@ -6166,16 +6163,16 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
+        <v>418</v>
+      </c>
+      <c r="B188" t="s">
+        <v>34</v>
+      </c>
+      <c r="C188" t="s">
+        <v>79</v>
+      </c>
+      <c r="D188" t="s">
         <v>419</v>
-      </c>
-      <c r="B188" t="s">
-        <v>35</v>
-      </c>
-      <c r="C188" t="s">
-        <v>80</v>
-      </c>
-      <c r="D188" t="s">
-        <v>420</v>
       </c>
       <c r="E188" t="s">
         <v>19</v>
@@ -6186,16 +6183,16 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>420</v>
+      </c>
+      <c r="B189" t="s">
+        <v>38</v>
+      </c>
+      <c r="C189" t="s">
+        <v>82</v>
+      </c>
+      <c r="D189" t="s">
         <v>421</v>
-      </c>
-      <c r="B189" t="s">
-        <v>39</v>
-      </c>
-      <c r="C189" t="s">
-        <v>83</v>
-      </c>
-      <c r="D189" t="s">
-        <v>422</v>
       </c>
       <c r="E189" t="s">
         <v>19</v>
@@ -6206,16 +6203,16 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
+        <v>422</v>
+      </c>
+      <c r="B190" t="s">
+        <v>42</v>
+      </c>
+      <c r="C190" t="s">
+        <v>85</v>
+      </c>
+      <c r="D190" t="s">
         <v>423</v>
-      </c>
-      <c r="B190" t="s">
-        <v>43</v>
-      </c>
-      <c r="C190" t="s">
-        <v>86</v>
-      </c>
-      <c r="D190" t="s">
-        <v>424</v>
       </c>
       <c r="E190" t="s">
         <v>19</v>
@@ -6226,7 +6223,7 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B191" t="s">
         <v>16</v>
@@ -6235,7 +6232,7 @@
         <v>17</v>
       </c>
       <c r="D191" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E191" t="s">
         <v>19</v>
@@ -6246,7 +6243,7 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B192" t="s">
         <v>22</v>
@@ -6255,7 +6252,7 @@
         <v>23</v>
       </c>
       <c r="D192" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E192" t="s">
         <v>19</v>
@@ -6266,27 +6263,27 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B193" t="s">
         <v>26</v>
       </c>
       <c r="C193" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D193" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E193" t="s">
         <v>19</v>
       </c>
       <c r="F193" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B194" t="s">
         <v>30</v>
@@ -6295,27 +6292,27 @@
         <v>31</v>
       </c>
       <c r="D194" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E194" t="s">
         <v>19</v>
       </c>
       <c r="F194" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
+        <v>432</v>
+      </c>
+      <c r="B195" t="s">
+        <v>34</v>
+      </c>
+      <c r="C195" t="s">
+        <v>35</v>
+      </c>
+      <c r="D195" t="s">
         <v>433</v>
-      </c>
-      <c r="B195" t="s">
-        <v>35</v>
-      </c>
-      <c r="C195" t="s">
-        <v>36</v>
-      </c>
-      <c r="D195" t="s">
-        <v>434</v>
       </c>
       <c r="E195" t="s">
         <v>19</v>
@@ -6326,16 +6323,16 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>434</v>
+      </c>
+      <c r="B196" t="s">
+        <v>38</v>
+      </c>
+      <c r="C196" t="s">
+        <v>39</v>
+      </c>
+      <c r="D196" t="s">
         <v>435</v>
-      </c>
-      <c r="B196" t="s">
-        <v>39</v>
-      </c>
-      <c r="C196" t="s">
-        <v>40</v>
-      </c>
-      <c r="D196" t="s">
-        <v>436</v>
       </c>
       <c r="E196" t="s">
         <v>19</v>
@@ -6346,16 +6343,16 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
+        <v>436</v>
+      </c>
+      <c r="B197" t="s">
+        <v>42</v>
+      </c>
+      <c r="C197" t="s">
+        <v>43</v>
+      </c>
+      <c r="D197" t="s">
         <v>437</v>
-      </c>
-      <c r="B197" t="s">
-        <v>43</v>
-      </c>
-      <c r="C197" t="s">
-        <v>44</v>
-      </c>
-      <c r="D197" t="s">
-        <v>438</v>
       </c>
       <c r="E197" t="s">
         <v>19</v>
@@ -6366,16 +6363,16 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B198" t="s">
         <v>16</v>
       </c>
       <c r="C198" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D198" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E198" t="s">
         <v>19</v>
@@ -6386,16 +6383,16 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B199" t="s">
         <v>22</v>
       </c>
       <c r="C199" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D199" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E199" t="s">
         <v>19</v>
@@ -6406,7 +6403,7 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B200" t="s">
         <v>26</v>
@@ -6415,7 +6412,7 @@
         <v>27</v>
       </c>
       <c r="D200" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E200" t="s">
         <v>19</v>
@@ -6426,16 +6423,16 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B201" t="s">
         <v>30</v>
       </c>
       <c r="C201" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D201" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="E201" t="s">
         <v>19</v>
@@ -6446,16 +6443,16 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>446</v>
+      </c>
+      <c r="B202" t="s">
+        <v>34</v>
+      </c>
+      <c r="C202" t="s">
+        <v>58</v>
+      </c>
+      <c r="D202" t="s">
         <v>447</v>
-      </c>
-      <c r="B202" t="s">
-        <v>35</v>
-      </c>
-      <c r="C202" t="s">
-        <v>59</v>
-      </c>
-      <c r="D202" t="s">
-        <v>448</v>
       </c>
       <c r="E202" t="s">
         <v>19</v>
@@ -6466,16 +6463,16 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
+        <v>448</v>
+      </c>
+      <c r="B203" t="s">
+        <v>38</v>
+      </c>
+      <c r="C203" t="s">
+        <v>61</v>
+      </c>
+      <c r="D203" t="s">
         <v>449</v>
-      </c>
-      <c r="B203" t="s">
-        <v>39</v>
-      </c>
-      <c r="C203" t="s">
-        <v>62</v>
-      </c>
-      <c r="D203" t="s">
-        <v>450</v>
       </c>
       <c r="E203" t="s">
         <v>19</v>
@@ -6486,16 +6483,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
+        <v>450</v>
+      </c>
+      <c r="B204" t="s">
+        <v>42</v>
+      </c>
+      <c r="C204" t="s">
+        <v>64</v>
+      </c>
+      <c r="D204" t="s">
         <v>451</v>
-      </c>
-      <c r="B204" t="s">
-        <v>43</v>
-      </c>
-      <c r="C204" t="s">
-        <v>65</v>
-      </c>
-      <c r="D204" t="s">
-        <v>452</v>
       </c>
       <c r="E204" t="s">
         <v>19</v>
@@ -6506,16 +6503,16 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B205" t="s">
         <v>16</v>
       </c>
       <c r="C205" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D205" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E205" t="s">
         <v>19</v>
@@ -6526,16 +6523,16 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B206" t="s">
         <v>22</v>
       </c>
       <c r="C206" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D206" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E206" t="s">
         <v>19</v>
@@ -6546,16 +6543,16 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B207" t="s">
         <v>26</v>
       </c>
       <c r="C207" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D207" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E207" t="s">
         <v>19</v>
@@ -6566,16 +6563,16 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B208" t="s">
         <v>30</v>
       </c>
       <c r="C208" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D208" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E208" t="s">
         <v>19</v>
@@ -6586,16 +6583,16 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
+        <v>460</v>
+      </c>
+      <c r="B209" t="s">
+        <v>34</v>
+      </c>
+      <c r="C209" t="s">
+        <v>79</v>
+      </c>
+      <c r="D209" t="s">
         <v>461</v>
-      </c>
-      <c r="B209" t="s">
-        <v>35</v>
-      </c>
-      <c r="C209" t="s">
-        <v>80</v>
-      </c>
-      <c r="D209" t="s">
-        <v>462</v>
       </c>
       <c r="E209" t="s">
         <v>19</v>
@@ -6606,16 +6603,16 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
+        <v>462</v>
+      </c>
+      <c r="B210" t="s">
+        <v>38</v>
+      </c>
+      <c r="C210" t="s">
+        <v>82</v>
+      </c>
+      <c r="D210" t="s">
         <v>463</v>
-      </c>
-      <c r="B210" t="s">
-        <v>39</v>
-      </c>
-      <c r="C210" t="s">
-        <v>83</v>
-      </c>
-      <c r="D210" t="s">
-        <v>464</v>
       </c>
       <c r="E210" t="s">
         <v>19</v>
@@ -6626,16 +6623,16 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
+        <v>464</v>
+      </c>
+      <c r="B211" t="s">
+        <v>42</v>
+      </c>
+      <c r="C211" t="s">
+        <v>85</v>
+      </c>
+      <c r="D211" t="s">
         <v>465</v>
-      </c>
-      <c r="B211" t="s">
-        <v>43</v>
-      </c>
-      <c r="C211" t="s">
-        <v>86</v>
-      </c>
-      <c r="D211" t="s">
-        <v>466</v>
       </c>
       <c r="E211" t="s">
         <v>19</v>
@@ -6646,7 +6643,7 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B212" t="s">
         <v>16</v>
@@ -6655,7 +6652,7 @@
         <v>17</v>
       </c>
       <c r="D212" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E212" t="s">
         <v>19</v>
@@ -6666,7 +6663,7 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B213" t="s">
         <v>22</v>
@@ -6675,7 +6672,7 @@
         <v>23</v>
       </c>
       <c r="D213" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E213" t="s">
         <v>19</v>
@@ -6686,16 +6683,16 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B214" t="s">
         <v>26</v>
       </c>
       <c r="C214" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D214" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E214" t="s">
         <v>19</v>
@@ -6706,7 +6703,7 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B215" t="s">
         <v>30</v>
@@ -6715,27 +6712,27 @@
         <v>31</v>
       </c>
       <c r="D215" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E215" t="s">
         <v>19</v>
       </c>
       <c r="F215" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
+        <v>474</v>
+      </c>
+      <c r="B216" t="s">
+        <v>34</v>
+      </c>
+      <c r="C216" t="s">
+        <v>35</v>
+      </c>
+      <c r="D216" t="s">
         <v>475</v>
-      </c>
-      <c r="B216" t="s">
-        <v>35</v>
-      </c>
-      <c r="C216" t="s">
-        <v>36</v>
-      </c>
-      <c r="D216" t="s">
-        <v>476</v>
       </c>
       <c r="E216" t="s">
         <v>19</v>
@@ -6746,16 +6743,16 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
+        <v>476</v>
+      </c>
+      <c r="B217" t="s">
+        <v>38</v>
+      </c>
+      <c r="C217" t="s">
+        <v>39</v>
+      </c>
+      <c r="D217" t="s">
         <v>477</v>
-      </c>
-      <c r="B217" t="s">
-        <v>39</v>
-      </c>
-      <c r="C217" t="s">
-        <v>40</v>
-      </c>
-      <c r="D217" t="s">
-        <v>478</v>
       </c>
       <c r="E217" t="s">
         <v>19</v>
@@ -6766,16 +6763,16 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>478</v>
+      </c>
+      <c r="B218" t="s">
+        <v>42</v>
+      </c>
+      <c r="C218" t="s">
+        <v>43</v>
+      </c>
+      <c r="D218" t="s">
         <v>479</v>
-      </c>
-      <c r="B218" t="s">
-        <v>43</v>
-      </c>
-      <c r="C218" t="s">
-        <v>44</v>
-      </c>
-      <c r="D218" t="s">
-        <v>480</v>
       </c>
       <c r="E218" t="s">
         <v>19</v>
@@ -6786,16 +6783,16 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B219" t="s">
         <v>16</v>
       </c>
       <c r="C219" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E219" t="s">
         <v>19</v>
@@ -6806,16 +6803,16 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B220" t="s">
         <v>22</v>
       </c>
       <c r="C220" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D220" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E220" t="s">
         <v>19</v>
@@ -6826,36 +6823,36 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B221" t="s">
         <v>26</v>
       </c>
       <c r="C221" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D221" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E221" t="s">
         <v>19</v>
       </c>
       <c r="F221" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B222" t="s">
         <v>30</v>
       </c>
       <c r="C222" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D222" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E222" t="s">
         <v>19</v>
@@ -6866,16 +6863,16 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
+        <v>488</v>
+      </c>
+      <c r="B223" t="s">
+        <v>34</v>
+      </c>
+      <c r="C223" t="s">
+        <v>58</v>
+      </c>
+      <c r="D223" t="s">
         <v>489</v>
-      </c>
-      <c r="B223" t="s">
-        <v>35</v>
-      </c>
-      <c r="C223" t="s">
-        <v>59</v>
-      </c>
-      <c r="D223" t="s">
-        <v>490</v>
       </c>
       <c r="E223" t="s">
         <v>19</v>
@@ -6886,16 +6883,16 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
+        <v>490</v>
+      </c>
+      <c r="B224" t="s">
+        <v>38</v>
+      </c>
+      <c r="C224" t="s">
+        <v>61</v>
+      </c>
+      <c r="D224" t="s">
         <v>491</v>
-      </c>
-      <c r="B224" t="s">
-        <v>39</v>
-      </c>
-      <c r="C224" t="s">
-        <v>62</v>
-      </c>
-      <c r="D224" t="s">
-        <v>492</v>
       </c>
       <c r="E224" t="s">
         <v>19</v>
@@ -6906,16 +6903,16 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
+        <v>492</v>
+      </c>
+      <c r="B225" t="s">
+        <v>42</v>
+      </c>
+      <c r="C225" t="s">
+        <v>64</v>
+      </c>
+      <c r="D225" t="s">
         <v>493</v>
-      </c>
-      <c r="B225" t="s">
-        <v>43</v>
-      </c>
-      <c r="C225" t="s">
-        <v>65</v>
-      </c>
-      <c r="D225" t="s">
-        <v>494</v>
       </c>
       <c r="E225" t="s">
         <v>19</v>
@@ -6926,16 +6923,16 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B226" t="s">
         <v>16</v>
       </c>
       <c r="C226" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D226" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E226" t="s">
         <v>19</v>
@@ -6946,16 +6943,16 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B227" t="s">
         <v>22</v>
       </c>
       <c r="C227" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D227" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E227" t="s">
         <v>19</v>
@@ -6966,7 +6963,7 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B228" t="s">
         <v>26</v>
@@ -6975,7 +6972,7 @@
         <v>27</v>
       </c>
       <c r="D228" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="E228" t="s">
         <v>19</v>
@@ -6986,16 +6983,16 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B229" t="s">
         <v>30</v>
       </c>
       <c r="C229" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D229" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="E229" t="s">
         <v>19</v>
@@ -7006,16 +7003,16 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
+        <v>502</v>
+      </c>
+      <c r="B230" t="s">
+        <v>34</v>
+      </c>
+      <c r="C230" t="s">
+        <v>79</v>
+      </c>
+      <c r="D230" t="s">
         <v>503</v>
-      </c>
-      <c r="B230" t="s">
-        <v>35</v>
-      </c>
-      <c r="C230" t="s">
-        <v>80</v>
-      </c>
-      <c r="D230" t="s">
-        <v>504</v>
       </c>
       <c r="E230" t="s">
         <v>19</v>
@@ -7026,16 +7023,16 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>504</v>
+      </c>
+      <c r="B231" t="s">
+        <v>38</v>
+      </c>
+      <c r="C231" t="s">
+        <v>82</v>
+      </c>
+      <c r="D231" t="s">
         <v>505</v>
-      </c>
-      <c r="B231" t="s">
-        <v>39</v>
-      </c>
-      <c r="C231" t="s">
-        <v>83</v>
-      </c>
-      <c r="D231" t="s">
-        <v>506</v>
       </c>
       <c r="E231" t="s">
         <v>19</v>
@@ -7046,16 +7043,16 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
+        <v>506</v>
+      </c>
+      <c r="B232" t="s">
+        <v>42</v>
+      </c>
+      <c r="C232" t="s">
+        <v>85</v>
+      </c>
+      <c r="D232" t="s">
         <v>507</v>
-      </c>
-      <c r="B232" t="s">
-        <v>43</v>
-      </c>
-      <c r="C232" t="s">
-        <v>86</v>
-      </c>
-      <c r="D232" t="s">
-        <v>508</v>
       </c>
       <c r="E232" t="s">
         <v>19</v>
@@ -7066,7 +7063,7 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B233" t="s">
         <v>16</v>
@@ -7075,7 +7072,7 @@
         <v>17</v>
       </c>
       <c r="D233" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E233" t="s">
         <v>19</v>
@@ -7086,7 +7083,7 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B234" t="s">
         <v>22</v>
@@ -7095,7 +7092,7 @@
         <v>23</v>
       </c>
       <c r="D234" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="E234" t="s">
         <v>19</v>
@@ -7106,16 +7103,16 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B235" t="s">
         <v>26</v>
       </c>
       <c r="C235" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D235" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E235" t="s">
         <v>19</v>
@@ -7126,7 +7123,7 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B236" t="s">
         <v>30</v>
@@ -7135,27 +7132,27 @@
         <v>31</v>
       </c>
       <c r="D236" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="E236" t="s">
         <v>19</v>
       </c>
       <c r="F236" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
+        <v>516</v>
+      </c>
+      <c r="B237" t="s">
+        <v>34</v>
+      </c>
+      <c r="C237" t="s">
+        <v>35</v>
+      </c>
+      <c r="D237" t="s">
         <v>517</v>
-      </c>
-      <c r="B237" t="s">
-        <v>35</v>
-      </c>
-      <c r="C237" t="s">
-        <v>36</v>
-      </c>
-      <c r="D237" t="s">
-        <v>518</v>
       </c>
       <c r="E237" t="s">
         <v>19</v>
@@ -7166,16 +7163,16 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
+        <v>518</v>
+      </c>
+      <c r="B238" t="s">
+        <v>38</v>
+      </c>
+      <c r="C238" t="s">
+        <v>39</v>
+      </c>
+      <c r="D238" t="s">
         <v>519</v>
-      </c>
-      <c r="B238" t="s">
-        <v>39</v>
-      </c>
-      <c r="C238" t="s">
-        <v>40</v>
-      </c>
-      <c r="D238" t="s">
-        <v>520</v>
       </c>
       <c r="E238" t="s">
         <v>19</v>
@@ -7186,16 +7183,16 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
+        <v>520</v>
+      </c>
+      <c r="B239" t="s">
+        <v>42</v>
+      </c>
+      <c r="C239" t="s">
+        <v>43</v>
+      </c>
+      <c r="D239" t="s">
         <v>521</v>
-      </c>
-      <c r="B239" t="s">
-        <v>43</v>
-      </c>
-      <c r="C239" t="s">
-        <v>44</v>
-      </c>
-      <c r="D239" t="s">
-        <v>522</v>
       </c>
       <c r="E239" t="s">
         <v>19</v>
@@ -7206,16 +7203,16 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B240" t="s">
         <v>16</v>
       </c>
       <c r="C240" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D240" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="E240" t="s">
         <v>19</v>
@@ -7226,16 +7223,16 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B241" t="s">
         <v>22</v>
       </c>
       <c r="C241" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D241" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="E241" t="s">
         <v>19</v>
@@ -7246,16 +7243,16 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B242" t="s">
         <v>26</v>
       </c>
       <c r="C242" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D242" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="E242" t="s">
         <v>19</v>
@@ -7266,16 +7263,16 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B243" t="s">
         <v>30</v>
       </c>
       <c r="C243" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D243" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="E243" t="s">
         <v>19</v>
@@ -7286,16 +7283,16 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
+        <v>530</v>
+      </c>
+      <c r="B244" t="s">
+        <v>34</v>
+      </c>
+      <c r="C244" t="s">
+        <v>58</v>
+      </c>
+      <c r="D244" t="s">
         <v>531</v>
-      </c>
-      <c r="B244" t="s">
-        <v>35</v>
-      </c>
-      <c r="C244" t="s">
-        <v>59</v>
-      </c>
-      <c r="D244" t="s">
-        <v>532</v>
       </c>
       <c r="E244" t="s">
         <v>19</v>
@@ -7306,16 +7303,16 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
+        <v>532</v>
+      </c>
+      <c r="B245" t="s">
+        <v>38</v>
+      </c>
+      <c r="C245" t="s">
+        <v>61</v>
+      </c>
+      <c r="D245" t="s">
         <v>533</v>
-      </c>
-      <c r="B245" t="s">
-        <v>39</v>
-      </c>
-      <c r="C245" t="s">
-        <v>62</v>
-      </c>
-      <c r="D245" t="s">
-        <v>534</v>
       </c>
       <c r="E245" t="s">
         <v>19</v>
@@ -7326,16 +7323,16 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
+        <v>534</v>
+      </c>
+      <c r="B246" t="s">
+        <v>42</v>
+      </c>
+      <c r="C246" t="s">
+        <v>64</v>
+      </c>
+      <c r="D246" t="s">
         <v>535</v>
-      </c>
-      <c r="B246" t="s">
-        <v>43</v>
-      </c>
-      <c r="C246" t="s">
-        <v>65</v>
-      </c>
-      <c r="D246" t="s">
-        <v>536</v>
       </c>
       <c r="E246" t="s">
         <v>19</v>
@@ -7346,16 +7343,16 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B247" t="s">
         <v>16</v>
       </c>
       <c r="C247" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D247" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="E247" t="s">
         <v>19</v>
@@ -7366,16 +7363,16 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B248" t="s">
         <v>22</v>
       </c>
       <c r="C248" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D248" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E248" t="s">
         <v>19</v>
@@ -7386,36 +7383,36 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B249" t="s">
         <v>26</v>
       </c>
       <c r="C249" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D249" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E249" t="s">
         <v>19</v>
       </c>
       <c r="F249" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B250" t="s">
         <v>30</v>
       </c>
       <c r="C250" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D250" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E250" t="s">
         <v>19</v>
@@ -7426,16 +7423,16 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
+        <v>544</v>
+      </c>
+      <c r="B251" t="s">
+        <v>34</v>
+      </c>
+      <c r="C251" t="s">
+        <v>79</v>
+      </c>
+      <c r="D251" t="s">
         <v>545</v>
-      </c>
-      <c r="B251" t="s">
-        <v>35</v>
-      </c>
-      <c r="C251" t="s">
-        <v>80</v>
-      </c>
-      <c r="D251" t="s">
-        <v>546</v>
       </c>
       <c r="E251" t="s">
         <v>19</v>
@@ -7446,16 +7443,16 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
+        <v>546</v>
+      </c>
+      <c r="B252" t="s">
+        <v>38</v>
+      </c>
+      <c r="C252" t="s">
+        <v>82</v>
+      </c>
+      <c r="D252" t="s">
         <v>547</v>
-      </c>
-      <c r="B252" t="s">
-        <v>39</v>
-      </c>
-      <c r="C252" t="s">
-        <v>83</v>
-      </c>
-      <c r="D252" t="s">
-        <v>548</v>
       </c>
       <c r="E252" t="s">
         <v>19</v>
@@ -7466,16 +7463,16 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
+        <v>548</v>
+      </c>
+      <c r="B253" t="s">
+        <v>42</v>
+      </c>
+      <c r="C253" t="s">
+        <v>85</v>
+      </c>
+      <c r="D253" t="s">
         <v>549</v>
-      </c>
-      <c r="B253" t="s">
-        <v>43</v>
-      </c>
-      <c r="C253" t="s">
-        <v>86</v>
-      </c>
-      <c r="D253" t="s">
-        <v>550</v>
       </c>
       <c r="E253" t="s">
         <v>19</v>
@@ -7486,7 +7483,7 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B254" t="s">
         <v>16</v>
@@ -7495,7 +7492,7 @@
         <v>17</v>
       </c>
       <c r="D254" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E254" t="s">
         <v>19</v>
@@ -7506,7 +7503,7 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B255" t="s">
         <v>22</v>
@@ -7515,7 +7512,7 @@
         <v>23</v>
       </c>
       <c r="D255" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E255" t="s">
         <v>19</v>
@@ -7526,7 +7523,7 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B256" t="s">
         <v>26</v>
@@ -7535,7 +7532,7 @@
         <v>27</v>
       </c>
       <c r="D256" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E256" t="s">
         <v>19</v>
@@ -7546,7 +7543,7 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B257" t="s">
         <v>30</v>
@@ -7555,27 +7552,27 @@
         <v>31</v>
       </c>
       <c r="D257" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="E257" t="s">
         <v>19</v>
       </c>
       <c r="F257" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
+        <v>558</v>
+      </c>
+      <c r="B258" t="s">
+        <v>34</v>
+      </c>
+      <c r="C258" t="s">
+        <v>35</v>
+      </c>
+      <c r="D258" t="s">
         <v>559</v>
-      </c>
-      <c r="B258" t="s">
-        <v>35</v>
-      </c>
-      <c r="C258" t="s">
-        <v>36</v>
-      </c>
-      <c r="D258" t="s">
-        <v>560</v>
       </c>
       <c r="E258" t="s">
         <v>19</v>
@@ -7586,16 +7583,16 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
+        <v>560</v>
+      </c>
+      <c r="B259" t="s">
+        <v>38</v>
+      </c>
+      <c r="C259" t="s">
+        <v>39</v>
+      </c>
+      <c r="D259" t="s">
         <v>561</v>
-      </c>
-      <c r="B259" t="s">
-        <v>39</v>
-      </c>
-      <c r="C259" t="s">
-        <v>40</v>
-      </c>
-      <c r="D259" t="s">
-        <v>562</v>
       </c>
       <c r="E259" t="s">
         <v>19</v>
@@ -7606,16 +7603,16 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
+        <v>562</v>
+      </c>
+      <c r="B260" t="s">
+        <v>42</v>
+      </c>
+      <c r="C260" t="s">
+        <v>43</v>
+      </c>
+      <c r="D260" t="s">
         <v>563</v>
-      </c>
-      <c r="B260" t="s">
-        <v>43</v>
-      </c>
-      <c r="C260" t="s">
-        <v>44</v>
-      </c>
-      <c r="D260" t="s">
-        <v>564</v>
       </c>
       <c r="E260" t="s">
         <v>19</v>
@@ -7626,16 +7623,16 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B261" t="s">
         <v>16</v>
       </c>
       <c r="C261" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D261" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E261" t="s">
         <v>19</v>
@@ -7646,16 +7643,16 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B262" t="s">
         <v>22</v>
       </c>
       <c r="C262" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D262" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E262" t="s">
         <v>19</v>
@@ -7666,16 +7663,16 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B263" t="s">
         <v>26</v>
       </c>
       <c r="C263" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D263" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="E263" t="s">
         <v>19</v>
@@ -7686,16 +7683,16 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B264" t="s">
         <v>30</v>
       </c>
       <c r="C264" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D264" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E264" t="s">
         <v>19</v>
@@ -7706,16 +7703,16 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
+        <v>572</v>
+      </c>
+      <c r="B265" t="s">
+        <v>34</v>
+      </c>
+      <c r="C265" t="s">
+        <v>58</v>
+      </c>
+      <c r="D265" t="s">
         <v>573</v>
-      </c>
-      <c r="B265" t="s">
-        <v>35</v>
-      </c>
-      <c r="C265" t="s">
-        <v>59</v>
-      </c>
-      <c r="D265" t="s">
-        <v>574</v>
       </c>
       <c r="E265" t="s">
         <v>19</v>
@@ -7726,16 +7723,16 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
+        <v>574</v>
+      </c>
+      <c r="B266" t="s">
+        <v>38</v>
+      </c>
+      <c r="C266" t="s">
+        <v>61</v>
+      </c>
+      <c r="D266" t="s">
         <v>575</v>
-      </c>
-      <c r="B266" t="s">
-        <v>39</v>
-      </c>
-      <c r="C266" t="s">
-        <v>62</v>
-      </c>
-      <c r="D266" t="s">
-        <v>576</v>
       </c>
       <c r="E266" t="s">
         <v>19</v>
@@ -7746,16 +7743,16 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
+        <v>576</v>
+      </c>
+      <c r="B267" t="s">
+        <v>42</v>
+      </c>
+      <c r="C267" t="s">
+        <v>64</v>
+      </c>
+      <c r="D267" t="s">
         <v>577</v>
-      </c>
-      <c r="B267" t="s">
-        <v>43</v>
-      </c>
-      <c r="C267" t="s">
-        <v>65</v>
-      </c>
-      <c r="D267" t="s">
-        <v>578</v>
       </c>
       <c r="E267" t="s">
         <v>19</v>
@@ -7766,16 +7763,16 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B268" t="s">
         <v>16</v>
       </c>
       <c r="C268" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D268" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E268" t="s">
         <v>19</v>
@@ -7786,16 +7783,16 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B269" t="s">
         <v>22</v>
       </c>
       <c r="C269" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D269" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="E269" t="s">
         <v>19</v>
@@ -7806,16 +7803,16 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B270" t="s">
         <v>26</v>
       </c>
       <c r="C270" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D270" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E270" t="s">
         <v>19</v>
@@ -7826,16 +7823,16 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B271" t="s">
         <v>30</v>
       </c>
       <c r="C271" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D271" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E271" t="s">
         <v>19</v>
@@ -7846,16 +7843,16 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
+        <v>586</v>
+      </c>
+      <c r="B272" t="s">
+        <v>34</v>
+      </c>
+      <c r="C272" t="s">
+        <v>79</v>
+      </c>
+      <c r="D272" t="s">
         <v>587</v>
-      </c>
-      <c r="B272" t="s">
-        <v>35</v>
-      </c>
-      <c r="C272" t="s">
-        <v>80</v>
-      </c>
-      <c r="D272" t="s">
-        <v>588</v>
       </c>
       <c r="E272" t="s">
         <v>19</v>
@@ -7866,16 +7863,16 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
+        <v>588</v>
+      </c>
+      <c r="B273" t="s">
+        <v>38</v>
+      </c>
+      <c r="C273" t="s">
+        <v>82</v>
+      </c>
+      <c r="D273" t="s">
         <v>589</v>
-      </c>
-      <c r="B273" t="s">
-        <v>39</v>
-      </c>
-      <c r="C273" t="s">
-        <v>83</v>
-      </c>
-      <c r="D273" t="s">
-        <v>590</v>
       </c>
       <c r="E273" t="s">
         <v>19</v>
@@ -7886,16 +7883,16 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
+        <v>590</v>
+      </c>
+      <c r="B274" t="s">
+        <v>42</v>
+      </c>
+      <c r="C274" t="s">
+        <v>85</v>
+      </c>
+      <c r="D274" t="s">
         <v>591</v>
-      </c>
-      <c r="B274" t="s">
-        <v>43</v>
-      </c>
-      <c r="C274" t="s">
-        <v>86</v>
-      </c>
-      <c r="D274" t="s">
-        <v>592</v>
       </c>
       <c r="E274" t="s">
         <v>19</v>
@@ -7906,7 +7903,7 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B275" t="s">
         <v>16</v>
@@ -7915,7 +7912,7 @@
         <v>17</v>
       </c>
       <c r="D275" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E275" t="s">
         <v>19</v>
@@ -7926,7 +7923,7 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B276" t="s">
         <v>22</v>
@@ -7935,7 +7932,7 @@
         <v>23</v>
       </c>
       <c r="D276" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E276" t="s">
         <v>19</v>
@@ -7946,27 +7943,27 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B277" t="s">
         <v>26</v>
       </c>
       <c r="C277" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D277" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E277" t="s">
         <v>19</v>
       </c>
       <c r="F277" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B278" t="s">
         <v>30</v>
@@ -7975,27 +7972,27 @@
         <v>31</v>
       </c>
       <c r="D278" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E278" t="s">
         <v>19</v>
       </c>
       <c r="F278" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
+        <v>600</v>
+      </c>
+      <c r="B279" t="s">
+        <v>34</v>
+      </c>
+      <c r="C279" t="s">
+        <v>35</v>
+      </c>
+      <c r="D279" t="s">
         <v>601</v>
-      </c>
-      <c r="B279" t="s">
-        <v>35</v>
-      </c>
-      <c r="C279" t="s">
-        <v>36</v>
-      </c>
-      <c r="D279" t="s">
-        <v>602</v>
       </c>
       <c r="E279" t="s">
         <v>19</v>
@@ -8006,16 +8003,16 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
+        <v>602</v>
+      </c>
+      <c r="B280" t="s">
+        <v>38</v>
+      </c>
+      <c r="C280" t="s">
+        <v>39</v>
+      </c>
+      <c r="D280" t="s">
         <v>603</v>
-      </c>
-      <c r="B280" t="s">
-        <v>39</v>
-      </c>
-      <c r="C280" t="s">
-        <v>40</v>
-      </c>
-      <c r="D280" t="s">
-        <v>604</v>
       </c>
       <c r="E280" t="s">
         <v>19</v>
@@ -8026,16 +8023,16 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
+        <v>604</v>
+      </c>
+      <c r="B281" t="s">
+        <v>42</v>
+      </c>
+      <c r="C281" t="s">
+        <v>43</v>
+      </c>
+      <c r="D281" t="s">
         <v>605</v>
-      </c>
-      <c r="B281" t="s">
-        <v>43</v>
-      </c>
-      <c r="C281" t="s">
-        <v>44</v>
-      </c>
-      <c r="D281" t="s">
-        <v>606</v>
       </c>
       <c r="E281" t="s">
         <v>19</v>
@@ -8046,16 +8043,16 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B282" t="s">
         <v>16</v>
       </c>
       <c r="C282" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D282" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="E282" t="s">
         <v>19</v>
@@ -8066,16 +8063,16 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B283" t="s">
         <v>22</v>
       </c>
       <c r="C283" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D283" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="E283" t="s">
         <v>19</v>
@@ -8086,7 +8083,7 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B284" t="s">
         <v>26</v>
@@ -8095,7 +8092,7 @@
         <v>27</v>
       </c>
       <c r="D284" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="E284" t="s">
         <v>19</v>
@@ -8106,16 +8103,16 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B285" t="s">
         <v>30</v>
       </c>
       <c r="C285" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D285" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="E285" t="s">
         <v>19</v>
@@ -8126,16 +8123,16 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
+        <v>614</v>
+      </c>
+      <c r="B286" t="s">
+        <v>34</v>
+      </c>
+      <c r="C286" t="s">
+        <v>58</v>
+      </c>
+      <c r="D286" t="s">
         <v>615</v>
-      </c>
-      <c r="B286" t="s">
-        <v>35</v>
-      </c>
-      <c r="C286" t="s">
-        <v>59</v>
-      </c>
-      <c r="D286" t="s">
-        <v>616</v>
       </c>
       <c r="E286" t="s">
         <v>19</v>
@@ -8146,16 +8143,16 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
+        <v>616</v>
+      </c>
+      <c r="B287" t="s">
+        <v>38</v>
+      </c>
+      <c r="C287" t="s">
+        <v>61</v>
+      </c>
+      <c r="D287" t="s">
         <v>617</v>
-      </c>
-      <c r="B287" t="s">
-        <v>39</v>
-      </c>
-      <c r="C287" t="s">
-        <v>62</v>
-      </c>
-      <c r="D287" t="s">
-        <v>618</v>
       </c>
       <c r="E287" t="s">
         <v>19</v>
@@ -8166,16 +8163,16 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
+        <v>618</v>
+      </c>
+      <c r="B288" t="s">
+        <v>42</v>
+      </c>
+      <c r="C288" t="s">
+        <v>64</v>
+      </c>
+      <c r="D288" t="s">
         <v>619</v>
-      </c>
-      <c r="B288" t="s">
-        <v>43</v>
-      </c>
-      <c r="C288" t="s">
-        <v>65</v>
-      </c>
-      <c r="D288" t="s">
-        <v>620</v>
       </c>
       <c r="E288" t="s">
         <v>19</v>
@@ -8186,16 +8183,16 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B289" t="s">
         <v>16</v>
       </c>
       <c r="C289" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D289" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="E289" t="s">
         <v>19</v>
@@ -8206,16 +8203,16 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B290" t="s">
         <v>22</v>
       </c>
       <c r="C290" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D290" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E290" t="s">
         <v>19</v>
@@ -8226,16 +8223,16 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B291" t="s">
         <v>26</v>
       </c>
       <c r="C291" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D291" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="E291" t="s">
         <v>19</v>
@@ -8246,16 +8243,16 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B292" t="s">
         <v>30</v>
       </c>
       <c r="C292" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D292" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="E292" t="s">
         <v>19</v>
@@ -8266,16 +8263,16 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
+        <v>628</v>
+      </c>
+      <c r="B293" t="s">
+        <v>34</v>
+      </c>
+      <c r="C293" t="s">
+        <v>79</v>
+      </c>
+      <c r="D293" t="s">
         <v>629</v>
-      </c>
-      <c r="B293" t="s">
-        <v>35</v>
-      </c>
-      <c r="C293" t="s">
-        <v>80</v>
-      </c>
-      <c r="D293" t="s">
-        <v>630</v>
       </c>
       <c r="E293" t="s">
         <v>19</v>
@@ -8286,16 +8283,16 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
+        <v>630</v>
+      </c>
+      <c r="B294" t="s">
+        <v>38</v>
+      </c>
+      <c r="C294" t="s">
+        <v>82</v>
+      </c>
+      <c r="D294" t="s">
         <v>631</v>
-      </c>
-      <c r="B294" t="s">
-        <v>39</v>
-      </c>
-      <c r="C294" t="s">
-        <v>83</v>
-      </c>
-      <c r="D294" t="s">
-        <v>632</v>
       </c>
       <c r="E294" t="s">
         <v>19</v>
@@ -8306,16 +8303,16 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
+        <v>632</v>
+      </c>
+      <c r="B295" t="s">
+        <v>42</v>
+      </c>
+      <c r="C295" t="s">
+        <v>85</v>
+      </c>
+      <c r="D295" t="s">
         <v>633</v>
-      </c>
-      <c r="B295" t="s">
-        <v>43</v>
-      </c>
-      <c r="C295" t="s">
-        <v>86</v>
-      </c>
-      <c r="D295" t="s">
-        <v>634</v>
       </c>
       <c r="E295" t="s">
         <v>19</v>
@@ -8326,7 +8323,7 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B296" t="s">
         <v>16</v>
@@ -8335,7 +8332,7 @@
         <v>17</v>
       </c>
       <c r="D296" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="E296" t="s">
         <v>19</v>
@@ -8346,7 +8343,7 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B297" t="s">
         <v>22</v>
@@ -8355,7 +8352,7 @@
         <v>23</v>
       </c>
       <c r="D297" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="E297" t="s">
         <v>19</v>
@@ -8366,16 +8363,16 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B298" t="s">
         <v>26</v>
       </c>
       <c r="C298" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D298" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="E298" t="s">
         <v>19</v>
@@ -8386,7 +8383,7 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B299" t="s">
         <v>30</v>
@@ -8395,27 +8392,27 @@
         <v>31</v>
       </c>
       <c r="D299" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="E299" t="s">
         <v>19</v>
       </c>
       <c r="F299" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
+        <v>642</v>
+      </c>
+      <c r="B300" t="s">
+        <v>34</v>
+      </c>
+      <c r="C300" t="s">
+        <v>35</v>
+      </c>
+      <c r="D300" t="s">
         <v>643</v>
-      </c>
-      <c r="B300" t="s">
-        <v>35</v>
-      </c>
-      <c r="C300" t="s">
-        <v>36</v>
-      </c>
-      <c r="D300" t="s">
-        <v>644</v>
       </c>
       <c r="E300" t="s">
         <v>19</v>
@@ -8426,16 +8423,16 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
+        <v>644</v>
+      </c>
+      <c r="B301" t="s">
+        <v>38</v>
+      </c>
+      <c r="C301" t="s">
+        <v>39</v>
+      </c>
+      <c r="D301" t="s">
         <v>645</v>
-      </c>
-      <c r="B301" t="s">
-        <v>39</v>
-      </c>
-      <c r="C301" t="s">
-        <v>40</v>
-      </c>
-      <c r="D301" t="s">
-        <v>646</v>
       </c>
       <c r="E301" t="s">
         <v>19</v>
